--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/6277-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/6277-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B8504823-3565-43F9-8B01-321043F32272}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6B2028E9-6554-489C-BFA0-82FCA17F561C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{E1FE8E92-6A18-4986-8A3F-A6CF2E005083}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{C31706F8-ECB4-4194-9A59-C7EE9CED48AA}"/>
   </bookViews>
   <sheets>
     <sheet name="6277-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1538,25 +1538,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35E6B7E0-1341-43DB-9074-72A9352CFA1B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{755A49BC-8591-4600-A3C5-5C1D99A0889A}">
   <dimension ref="A1:R68"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" customWidth="1"/>
-    <col min="3" max="3" width="8.5546875" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="7" width="8.33203125" customWidth="1"/>
-    <col min="8" max="8" width="8" customWidth="1"/>
-    <col min="9" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.33203125" customWidth="1"/>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="2" max="2" width="10.875" customWidth="1"/>
+    <col min="3" max="3" width="10.625" customWidth="1"/>
+    <col min="4" max="4" width="10.375" customWidth="1"/>
+    <col min="5" max="5" width="9.875" customWidth="1"/>
+    <col min="6" max="7" width="10.375" customWidth="1"/>
+    <col min="8" max="8" width="9.875" customWidth="1"/>
+    <col min="9" max="10" width="10.375" customWidth="1"/>
+    <col min="11" max="13" width="9.875" customWidth="1"/>
+    <col min="14" max="14" width="10.375" customWidth="1"/>
+    <col min="15" max="17" width="9.875" customWidth="1"/>
+    <col min="18" max="18" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1584,7 +1584,7 @@
       <c r="Q1" s="30"/>
       <c r="R1" s="22"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1614,7 +1614,7 @@
       <c r="Q2" s="32"/>
       <c r="R2" s="33"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1660,7 +1660,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1710,7 +1710,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="37">
         <v>2026</v>
       </c>
@@ -1764,7 +1764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>26</v>
       </c>
@@ -1820,7 +1820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="39">
         <v>2025</v>
       </c>
@@ -1874,7 +1874,7 @@
         <v>5.0199999999999996</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="s">
         <v>26</v>
       </c>
@@ -1930,7 +1930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>26</v>
       </c>
@@ -1986,7 +1986,7 @@
         <v>1.54</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
         <v>26</v>
       </c>
@@ -2042,7 +2042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="17" t="s">
         <v>26</v>
       </c>
@@ -2098,7 +2098,7 @@
         <v>3.48</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="17" t="s">
         <v>26</v>
       </c>
@@ -2154,7 +2154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="37">
         <v>2024</v>
       </c>
@@ -2208,7 +2208,7 @@
         <v>4.92</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>26</v>
       </c>
@@ -2264,7 +2264,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>26</v>
       </c>
@@ -2320,7 +2320,7 @@
         <v>2.1800000000000002</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>26</v>
       </c>
@@ -2376,7 +2376,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>26</v>
       </c>
@@ -2432,7 +2432,7 @@
         <v>2.74</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>26</v>
       </c>
@@ -2488,7 +2488,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="39">
         <v>2023</v>
       </c>
@@ -2542,7 +2542,7 @@
         <v>6.34</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="17" t="s">
         <v>26</v>
       </c>
@@ -2598,7 +2598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="s">
         <v>26</v>
       </c>
@@ -2654,7 +2654,7 @@
         <v>2.59</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="17" t="s">
         <v>26</v>
       </c>
@@ -2710,7 +2710,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="17" t="s">
         <v>26</v>
       </c>
@@ -2766,7 +2766,7 @@
         <v>3.75</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="17" t="s">
         <v>26</v>
       </c>
@@ -2822,7 +2822,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="37">
         <v>2022</v>
       </c>
@@ -2876,7 +2876,7 @@
         <v>6.82</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
         <v>26</v>
       </c>
@@ -2932,7 +2932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>26</v>
       </c>
@@ -2988,7 +2988,7 @@
         <v>3.07</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
         <v>26</v>
       </c>
@@ -3044,7 +3044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
         <v>26</v>
       </c>
@@ -3100,7 +3100,7 @@
         <v>3.75</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
         <v>26</v>
       </c>
@@ -3156,7 +3156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="39">
         <v>2021</v>
       </c>
@@ -3210,7 +3210,7 @@
         <v>6.25</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="17" t="s">
         <v>26</v>
       </c>
@@ -3266,7 +3266,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="17" t="s">
         <v>26</v>
       </c>
@@ -3322,7 +3322,7 @@
         <v>2.73</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="17" t="s">
         <v>26</v>
       </c>
@@ -3378,7 +3378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="17" t="s">
         <v>26</v>
       </c>
@@ -3434,7 +3434,7 @@
         <v>3.52</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="17" t="s">
         <v>26</v>
       </c>
@@ -3490,7 +3490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="37">
         <v>2020</v>
       </c>
@@ -3544,7 +3544,7 @@
         <v>8.83</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="11" t="s">
         <v>26</v>
       </c>
@@ -3600,7 +3600,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="11" t="s">
         <v>26</v>
       </c>
@@ -3656,7 +3656,7 @@
         <v>2.94</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="11" t="s">
         <v>26</v>
       </c>
@@ -3712,7 +3712,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="11" t="s">
         <v>26</v>
       </c>
@@ -3768,7 +3768,7 @@
         <v>5.89</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="39">
         <v>2019</v>
       </c>
@@ -3822,7 +3822,7 @@
         <v>8.56</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="17" t="s">
         <v>26</v>
       </c>
@@ -3878,7 +3878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="17" t="s">
         <v>26</v>
       </c>
@@ -3934,7 +3934,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="17" t="s">
         <v>26</v>
       </c>
@@ -3990,7 +3990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="17" t="s">
         <v>26</v>
       </c>
@@ -4046,7 +4046,7 @@
         <v>8.56</v>
       </c>
     </row>
-    <row r="47" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="37">
         <v>2018</v>
       </c>
@@ -4100,7 +4100,7 @@
         <v>6.12</v>
       </c>
     </row>
-    <row r="48" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="39">
         <v>2017</v>
       </c>
@@ -4154,7 +4154,7 @@
         <v>6.79</v>
       </c>
     </row>
-    <row r="49" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="37">
         <v>2016</v>
       </c>
@@ -4208,7 +4208,7 @@
         <v>5.96</v>
       </c>
     </row>
-    <row r="50" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="39">
         <v>2015</v>
       </c>
@@ -4262,7 +4262,7 @@
         <v>6.63</v>
       </c>
     </row>
-    <row r="51" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A51" s="37">
         <v>2014</v>
       </c>
@@ -4316,7 +4316,7 @@
         <v>5.85</v>
       </c>
     </row>
-    <row r="52" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A52" s="39">
         <v>2013</v>
       </c>
@@ -4370,7 +4370,7 @@
         <v>5.56</v>
       </c>
     </row>
-    <row r="53" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A53" s="37">
         <v>2012</v>
       </c>
@@ -4424,7 +4424,7 @@
         <v>6.31</v>
       </c>
     </row>
-    <row r="54" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A54" s="39">
         <v>2011</v>
       </c>
@@ -4478,7 +4478,7 @@
         <v>6.27</v>
       </c>
     </row>
-    <row r="55" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A55" s="37">
         <v>2010</v>
       </c>
@@ -4532,7 +4532,7 @@
         <v>5.26</v>
       </c>
     </row>
-    <row r="56" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A56" s="39">
         <v>2009</v>
       </c>
@@ -4586,7 +4586,7 @@
         <v>6.69</v>
       </c>
     </row>
-    <row r="57" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A57" s="37">
         <v>2008</v>
       </c>
@@ -4640,7 +4640,7 @@
         <v>8.15</v>
       </c>
     </row>
-    <row r="58" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A58" s="39">
         <v>2007</v>
       </c>
@@ -4694,7 +4694,7 @@
         <v>3.68</v>
       </c>
     </row>
-    <row r="59" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A59" s="37">
         <v>2006</v>
       </c>
@@ -4748,7 +4748,7 @@
         <v>5.49</v>
       </c>
     </row>
-    <row r="60" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A60" s="39">
         <v>2005</v>
       </c>
@@ -4802,7 +4802,7 @@
         <v>7.23</v>
       </c>
     </row>
-    <row r="61" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A61" s="37">
         <v>2004</v>
       </c>
@@ -4856,7 +4856,7 @@
         <v>5.53</v>
       </c>
     </row>
-    <row r="62" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A62" s="39">
         <v>2003</v>
       </c>
@@ -4910,7 +4910,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="63" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A63" s="37">
         <v>2002</v>
       </c>
@@ -4964,7 +4964,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="64" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A64" s="39">
         <v>2001</v>
       </c>
@@ -5018,7 +5018,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="65" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A65" s="37">
         <v>2000</v>
       </c>
@@ -5072,7 +5072,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="66" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A66" s="39">
         <v>1999</v>
       </c>
@@ -5126,7 +5126,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="67" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A67" s="37">
         <v>1998</v>
       </c>
@@ -5180,7 +5180,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="68" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A68" s="39" t="s">
         <v>65</v>
       </c>
